--- a/tests/modules/bsee/analysis/results/drilling_and_completion_days_by_api_latest.xlsx
+++ b/tests/modules/bsee/analysis/results/drilling_and_completion_days_by_api_latest.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L34"/>
+  <dimension ref="A1:L35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1481,53 +1481,53 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>St Malo</t>
+          <t>Shenandoah</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>18745</t>
+          <t>31938</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>6820</t>
+          <t>5800</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>608124005300</t>
+          <t>608124014400</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>PN001</t>
+          <t>SA009</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>12/11/2011</t>
+          <t>01/29/2023</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>10/16/2012</t>
+          <t>05/12/2023</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>310</v>
+        <v>103</v>
       </c>
       <c r="I21" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J21" t="n">
-        <v>29009</v>
+        <v>31870</v>
       </c>
       <c r="K21" t="n">
-        <v>28093</v>
+        <v>31085</v>
       </c>
       <c r="L21" t="n">
-        <v>14.1</v>
+        <v>15.4</v>
       </c>
     </row>
     <row r="22">
@@ -1538,7 +1538,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>18753</t>
+          <t>18745</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1548,38 +1548,38 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>608124005600</t>
+          <t>608124005300</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>PS003</t>
+          <t>PN001</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>02/05/2012</t>
+          <t>12/11/2011</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>03/16/2012</t>
+          <t>10/16/2012</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>40</v>
+        <v>310</v>
       </c>
       <c r="I22" t="n">
         <v>0</v>
       </c>
       <c r="J22" t="n">
-        <v>28276</v>
+        <v>29009</v>
       </c>
       <c r="K22" t="n">
-        <v>28049</v>
+        <v>28093</v>
       </c>
       <c r="L22" t="n">
-        <v>14.6</v>
+        <v>14.1</v>
       </c>
     </row>
     <row r="23">
@@ -1600,38 +1600,38 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>608124011400</t>
+          <t>608124005600</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>PS002</t>
+          <t>PS003</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>01/15/2017</t>
+          <t>02/05/2012</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>02/12/2017</t>
+          <t>03/16/2012</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="I23" t="n">
         <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>29401</v>
+        <v>28276</v>
       </c>
       <c r="K23" t="n">
-        <v>28265</v>
+        <v>28049</v>
       </c>
       <c r="L23" t="n">
-        <v>14</v>
+        <v>14.6</v>
       </c>
     </row>
     <row r="24">
@@ -1652,38 +1652,38 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>608124013600</t>
+          <t>608124011400</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>PS006</t>
+          <t>PS002</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>05/23/2021</t>
+          <t>01/15/2017</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>05/27/2021</t>
+          <t>02/12/2017</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>4</v>
+        <v>28</v>
       </c>
       <c r="I24" t="n">
         <v>0</v>
       </c>
       <c r="J24" t="n">
-        <v>31295</v>
+        <v>29401</v>
       </c>
       <c r="K24" t="n">
-        <v>28590</v>
+        <v>28265</v>
       </c>
       <c r="L24" t="n">
-        <v>14.1</v>
+        <v>14</v>
       </c>
     </row>
     <row r="25">
@@ -1704,35 +1704,35 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>608124015100</t>
+          <t>608124013600</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>PS008</t>
+          <t>PS006</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>11/19/2023</t>
+          <t>05/23/2021</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>11/21/2023</t>
+          <t>05/27/2021</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I25" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="J25" t="n">
-        <v>28695</v>
+        <v>31295</v>
       </c>
       <c r="K25" t="n">
-        <v>28015</v>
+        <v>28590</v>
       </c>
       <c r="L25" t="n">
         <v>14.1</v>
@@ -1741,50 +1741,50 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Stones</t>
+          <t>St Malo</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>17001</t>
+          <t>18753</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>9525</t>
+          <t>6820</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>608124007700</t>
+          <t>608124015100</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>001</t>
+          <t>PS008</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>10/14/2012</t>
+          <t>11/19/2023</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>10/21/2012</t>
+          <t>11/21/2023</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="I26" t="n">
         <v>6</v>
       </c>
       <c r="J26" t="n">
-        <v>29571</v>
+        <v>28695</v>
       </c>
       <c r="K26" t="n">
-        <v>28076</v>
+        <v>28015</v>
       </c>
       <c r="L26" t="n">
         <v>14.1</v>
@@ -1808,38 +1808,38 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>608124009200</t>
+          <t>608124007700</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>005</t>
+          <t>001</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>03/23/2014</t>
+          <t>10/14/2012</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>03/26/2014</t>
+          <t>10/21/2012</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="I27" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J27" t="n">
-        <v>20525</v>
+        <v>29571</v>
       </c>
       <c r="K27" t="n">
-        <v>18865</v>
+        <v>28076</v>
       </c>
       <c r="L27" t="n">
-        <v>16.2</v>
+        <v>14.1</v>
       </c>
     </row>
     <row r="28">
@@ -1860,7 +1860,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>608124009201</t>
+          <t>608124009200</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1870,28 +1870,28 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>06/15/2014</t>
+          <t>03/23/2014</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>06/21/2014</t>
+          <t>03/26/2014</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="I28" t="n">
         <v>0</v>
       </c>
       <c r="J28" t="n">
-        <v>25585</v>
+        <v>20525</v>
       </c>
       <c r="K28" t="n">
-        <v>22868</v>
+        <v>18865</v>
       </c>
       <c r="L28" t="n">
-        <v>11.1</v>
+        <v>16.2</v>
       </c>
     </row>
     <row r="29">
@@ -1912,38 +1912,38 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>608124010400</t>
+          <t>608124009201</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>SN208</t>
+          <t>005</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>08/05/2015</t>
+          <t>06/15/2014</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>02/20/2017</t>
+          <t>06/21/2014</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>565</v>
+        <v>6</v>
       </c>
       <c r="I29" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="J29" t="n">
-        <v>27840</v>
+        <v>25585</v>
       </c>
       <c r="K29" t="n">
-        <v>27326</v>
+        <v>22868</v>
       </c>
       <c r="L29" t="n">
-        <v>14</v>
+        <v>11.1</v>
       </c>
     </row>
     <row r="30">
@@ -1964,38 +1964,38 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>608124011000</t>
+          <t>608124010400</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>011</t>
+          <t>SN208</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>05/10/2016</t>
+          <t>08/05/2015</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>07/28/2016</t>
+          <t>02/20/2017</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>79</v>
+        <v>565</v>
       </c>
       <c r="I30" t="n">
         <v>6</v>
       </c>
       <c r="J30" t="n">
-        <v>29050</v>
+        <v>27840</v>
       </c>
       <c r="K30" t="n">
-        <v>28126</v>
+        <v>27326</v>
       </c>
       <c r="L30" t="n">
-        <v>13.7</v>
+        <v>14</v>
       </c>
     </row>
     <row r="31">
@@ -2016,38 +2016,38 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>608124011001</t>
+          <t>608124011000</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>SN110</t>
+          <t>011</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>08/28/2016</t>
+          <t>05/10/2016</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>09/08/2016</t>
+          <t>07/28/2016</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>11</v>
+        <v>79</v>
       </c>
       <c r="I31" t="n">
-        <v>23</v>
+        <v>6</v>
       </c>
       <c r="J31" t="n">
-        <v>28075</v>
+        <v>29050</v>
       </c>
       <c r="K31" t="n">
-        <v>27228</v>
+        <v>28126</v>
       </c>
       <c r="L31" t="n">
-        <v>14</v>
+        <v>13.7</v>
       </c>
     </row>
     <row r="32">
@@ -2068,38 +2068,38 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>608124011200</t>
+          <t>608124011001</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>SN206</t>
+          <t>SN110</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>12/05/2016</t>
+          <t>08/28/2016</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>08/21/2017</t>
+          <t>09/08/2016</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>259</v>
+        <v>11</v>
       </c>
       <c r="I32" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="J32" t="n">
-        <v>30717</v>
+        <v>28075</v>
       </c>
       <c r="K32" t="n">
-        <v>27172</v>
+        <v>27228</v>
       </c>
       <c r="L32" t="n">
-        <v>14.3</v>
+        <v>14</v>
       </c>
     </row>
     <row r="33">
@@ -2120,38 +2120,38 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>608124011700</t>
+          <t>608124011200</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>SN207</t>
+          <t>SN206</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>04/30/2017</t>
+          <t>12/05/2016</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>06/03/2017</t>
+          <t>08/21/2017</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>34</v>
+        <v>259</v>
       </c>
       <c r="I33" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="J33" t="n">
-        <v>31080</v>
+        <v>30717</v>
       </c>
       <c r="K33" t="n">
-        <v>28179</v>
+        <v>27172</v>
       </c>
       <c r="L33" t="n">
-        <v>14</v>
+        <v>14.3</v>
       </c>
     </row>
     <row r="34">
@@ -2172,37 +2172,89 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
+          <t>608124011700</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>SN207</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>04/30/2017</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>06/03/2017</t>
+        </is>
+      </c>
+      <c r="H34" t="n">
+        <v>34</v>
+      </c>
+      <c r="I34" t="n">
+        <v>6</v>
+      </c>
+      <c r="J34" t="n">
+        <v>31080</v>
+      </c>
+      <c r="K34" t="n">
+        <v>28179</v>
+      </c>
+      <c r="L34" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Stones</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>17001</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>9525</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
           <t>608124013400</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr">
+      <c r="E35" t="inlineStr">
         <is>
           <t>SN216</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr">
+      <c r="F35" t="inlineStr">
         <is>
           <t>12/13/2020</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr">
+      <c r="G35" t="inlineStr">
         <is>
           <t>02/27/2021</t>
         </is>
       </c>
-      <c r="H34" t="n">
+      <c r="H35" t="n">
         <v>76</v>
       </c>
-      <c r="I34" t="n">
+      <c r="I35" t="n">
         <v>4</v>
       </c>
-      <c r="J34" t="n">
+      <c r="J35" t="n">
         <v>28283</v>
       </c>
-      <c r="K34" t="n">
+      <c r="K35" t="n">
         <v>27595</v>
       </c>
-      <c r="L34" t="n">
+      <c r="L35" t="n">
         <v>13.9</v>
       </c>
     </row>
